--- a/output/第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx
+++ b/output/第10期計画_給付費データ・地域支援事業実施報告の受領点検.xlsx
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>第6章第3節2（地域支援事業の量の見込み）</t>
+          <t>第5章 基本目標2（認知症施策）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の実績を据え置いて延ばしている</t>
+          <t>認知症初期集中支援推進事業の実施状況の記載がない</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況を確認できたことを注記する。量の見込みは単位が違うため据え置きのままとする</t>
+          <t>構成3町が担当チームを設置していること、令和7年度は美瑛町が対応件数0件で医師を確保できず休止していることを現状と課題・関連データ・施策の方向性・主な事業に加える</t>
         </is>
       </c>
     </row>
@@ -1187,22 +1187,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>町別データシート</t>
+          <t>計画素案</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>給付費の表の注</t>
+          <t>第6章第3節2（地域支援事業の量の見込み）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>3町の合計と広域連合単位の値に差がある</t>
+          <t>令和6年度の実績を据え置いて延ばしている</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>差が解消した旨に改める</t>
+          <t>令和7年度の実施状況を確認できたことを注記する。量の見込みは単位が違うため据え置きのままとする</t>
         </is>
       </c>
     </row>
@@ -1212,22 +1212,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量算定</t>
+          <t>町別データシート</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>01シート（出所による差）・11シート</t>
+          <t>給付費の表の注</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>令和7年度のみ4.0％の差がある</t>
+          <t>3町の合計と広域連合単位の値に差がある</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>差が解消した旨に改め、給付費データが審査年月ベースであることを併せて示す</t>
+          <t>差が解消した旨に改める</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>見込量算定に要する資料と電話照会</t>
+          <t>サービス見込量算定</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>第2節（給付費データの差）</t>
+          <t>01シート（出所による差）・11シート</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>どの条件で抽出したものかを照会する</t>
+          <t>令和7年度のみ4.0％の差がある</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>照会の要はなくなった。節を受領済みとして改める</t>
+          <t>差が解消した旨に改め、給付費データが審査年月ベースであることを併せて示す</t>
         </is>
       </c>
     </row>
@@ -1262,182 +1262,207 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>見込量算定に要する資料と電話照会</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>第2節（給付費データの差）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>どの条件で抽出したものかを照会する</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>照会の要はなくなった。節を受領済みとして改める</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>季節性と施策反映</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>単価の伸びの分母</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>分母を3町合計に採ると＋1.63％、広域連合単位なら＋5.90％</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>分母が一つに定まったため一本化する</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　確認事項の状態</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>確認事項</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>従前</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>本件の受領後</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>残るもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>No.87　給付費データ 令和7年度の差</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>未解決</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>解決（再提供を受けたファイルにより差が解消した）</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>なし</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>No.112　地域支援事業の量の見込み</t>
+          <t>No.87　給付費データ 令和7年度の差</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>総合事業の令和7年度実績が未受領</t>
+          <t>未解決</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>一部解決（事業ごとの実施状況と量を確認できた）</t>
+          <t>解決（再提供を受けたファイルにより差が解消した）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>事業ごとの利用者実人数（年間）と事業費</t>
+          <t>なし</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>No.150　認知症総合支援事業の実績</t>
+          <t>No.112　地域支援事業の量の見込み</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>実績が未受領</t>
+          <t>総合事業の令和7年度実績が未受領</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>一部解決（取組の回数を町別に確認できた）</t>
+          <t>一部解決（事業ごとの実施状況と量を確認できた）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>6事業別の事業費</t>
+          <t>事業ごとの利用者実人数（年間）と事業費</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>No.118からNo.122　地域ケア会議</t>
+          <t>No.150　認知症総合支援事業の実績</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>開催回数のみで町別の値がない</t>
+          <t>実績が未受領</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>一部解決（美瑛町・東川町の開催回数を確認できた）</t>
+          <t>一部解決（取組の回数を町別に確認できた）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>3町で単位がそろっていない。代表KPI O2の基準値</t>
+          <t>6事業別の事業費</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>No.118からNo.122　地域ケア会議</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>開催回数のみで町別の値がない</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>一部解決（美瑛町・東川町の開催回数を確認できた）</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>3町で単位がそろっていない。代表KPI O2の基準値</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>No.5　地域支援事業の実績</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>未受領</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>一部解決（量は確認できた）</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>費用の額</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>本件により新たな確認事項は起こしていません。</t>
         </is>
@@ -1446,9 +1471,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
